--- a/outputs/Block5_Popular_Vote.xlsx
+++ b/outputs/Block5_Popular_Vote.xlsx
@@ -408,10 +408,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="C2">
-        <v>50.93</v>
+        <v>52.07</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -419,10 +419,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="C3">
-        <v>46.15</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="4" spans="1:3">
